--- a/artfynd/A 38418-2021 artfynd.xlsx
+++ b/artfynd/A 38418-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38418-2021 artfynd.xlsx
+++ b/artfynd/A 38418-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5027196</v>
+        <v>83764</v>
       </c>
       <c r="B2" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ludgo, nära Malmviks skola, Srm</t>
+          <t>Rågången, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619912.9100207228</v>
+        <v>620047</v>
       </c>
       <c r="R2" t="n">
-        <v>6540295.327620516</v>
+        <v>6540164</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2006-08-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2006-08-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,21 +760,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>lövskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Anneli Kihl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Anneli Kihl, Staffan Kihl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,12 +779,7 @@
         <v>4805417</v>
       </c>
       <c r="B3" t="n">
-        <v>101679</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>619912.9100207228</v>
+        <v>619913</v>
       </c>
       <c r="R3" t="n">
-        <v>6540295.327620516</v>
+        <v>6540295</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,19 +844,9 @@
           <t>2006-08-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2006-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,6 +875,205 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4806395</v>
+      </c>
+      <c r="B4" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>250 m NV Rågången, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>619913</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6540320</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ludgo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2007-04-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2007-05-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anneli Kihl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anneli Kihl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5027196</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ludgo, nära Malmviks skola, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>619913</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6540295</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ludgo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2006-08-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2006-08-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
